--- a/outputs/41420.xlsx
+++ b/outputs/41420.xlsx
@@ -127,19 +127,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -341,23 +341,23 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A2&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A2&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
         <v>5</v>
       </c>
       <c r="E2" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A2&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
       <c r="F2" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A2&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
       <c r="G2" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A2&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A2&amp;""))+ISNUMBER(SEARCH("1",$A2&amp;""))+ISNUMBER(SEARCH("2",$A2&amp;""))+ISNUMBER(SEARCH("3",$A2&amp;""))+ISNUMBER(SEARCH("4",$A2&amp;""))+ISNUMBER(SEARCH("5",$A2&amp;""))+ISNUMBER(SEARCH("6",$A2&amp;""))+ISNUMBER(SEARCH("7",$A2&amp;""))+ISNUMBER(SEARCH("8",$A2&amp;""))+ISNUMBER(SEARCH("9",$A2&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>
@@ -367,23 +367,23 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A3&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A3&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
         <v>4</v>
       </c>
       <c r="E3" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A3&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
         <v>7</v>
       </c>
       <c r="F3" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A3&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
         <v>8</v>
       </c>
       <c r="G3" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A3&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A3&amp;""))+ISNUMBER(SEARCH("1",$A3&amp;""))+ISNUMBER(SEARCH("2",$A3&amp;""))+ISNUMBER(SEARCH("3",$A3&amp;""))+ISNUMBER(SEARCH("4",$A3&amp;""))+ISNUMBER(SEARCH("5",$A3&amp;""))+ISNUMBER(SEARCH("6",$A3&amp;""))+ISNUMBER(SEARCH("7",$A3&amp;""))+ISNUMBER(SEARCH("8",$A3&amp;""))+ISNUMBER(SEARCH("9",$A3&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>
@@ -393,23 +393,23 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A4&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
         <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A4&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A4&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
         <v>7</v>
       </c>
       <c r="F4" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A4&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
       <c r="G4" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A4&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A4&amp;""))+ISNUMBER(SEARCH("1",$A4&amp;""))+ISNUMBER(SEARCH("2",$A4&amp;""))+ISNUMBER(SEARCH("3",$A4&amp;""))+ISNUMBER(SEARCH("4",$A4&amp;""))+ISNUMBER(SEARCH("5",$A4&amp;""))+ISNUMBER(SEARCH("6",$A4&amp;""))+ISNUMBER(SEARCH("7",$A4&amp;""))+ISNUMBER(SEARCH("8",$A4&amp;""))+ISNUMBER(SEARCH("9",$A4&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>
@@ -419,23 +419,23 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A5&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A5&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
         <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A5&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
         <v>6</v>
       </c>
       <c r="F5" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A5&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
         <v>8</v>
       </c>
       <c r="G5" s="4" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A5&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A5&amp;""))+ISNUMBER(SEARCH("1",$A5&amp;""))+ISNUMBER(SEARCH("2",$A5&amp;""))+ISNUMBER(SEARCH("3",$A5&amp;""))+ISNUMBER(SEARCH("4",$A5&amp;""))+ISNUMBER(SEARCH("5",$A5&amp;""))+ISNUMBER(SEARCH("6",$A5&amp;""))+ISNUMBER(SEARCH("7",$A5&amp;""))+ISNUMBER(SEARCH("8",$A5&amp;""))+ISNUMBER(SEARCH("9",$A5&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>
@@ -445,23 +445,23 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A6&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A6&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
         <v>2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A6&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
         <v>4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A6&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
         <v>9</v>
       </c>
       <c r="G6" s="4" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A6&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A6&amp;""))+ISNUMBER(SEARCH("1",$A6&amp;""))+ISNUMBER(SEARCH("2",$A6&amp;""))+ISNUMBER(SEARCH("3",$A6&amp;""))+ISNUMBER(SEARCH("4",$A6&amp;""))+ISNUMBER(SEARCH("5",$A6&amp;""))+ISNUMBER(SEARCH("6",$A6&amp;""))+ISNUMBER(SEARCH("7",$A6&amp;""))+ISNUMBER(SEARCH("8",$A6&amp;""))+ISNUMBER(SEARCH("9",$A6&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>
@@ -471,23 +471,23 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A7&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A7&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A7&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
         <v>6</v>
       </c>
       <c r="F7" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A7&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
       <c r="G7" s="4" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A7&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A7&amp;""))+ISNUMBER(SEARCH("1",$A7&amp;""))+ISNUMBER(SEARCH("2",$A7&amp;""))+ISNUMBER(SEARCH("3",$A7&amp;""))+ISNUMBER(SEARCH("4",$A7&amp;""))+ISNUMBER(SEARCH("5",$A7&amp;""))+ISNUMBER(SEARCH("6",$A7&amp;""))+ISNUMBER(SEARCH("7",$A7&amp;""))+ISNUMBER(SEARCH("8",$A7&amp;""))+ISNUMBER(SEARCH("9",$A7&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>
@@ -497,23 +497,23 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;"")))&lt;1,"",IF(ISNUMBER(SEARCH("0",$A8&amp;""))&gt;=1,0,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))&gt;=1,1,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))&gt;=1,2,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))&gt;=1,3,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))&gt;=1,4,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))&gt;=1,5,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))&gt;=1,6,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))&gt;=1,7,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))&gt;=1,8,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;""))&gt;=1,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
         <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;"")))&lt;2,"",IF(ISNUMBER(SEARCH("0",$A8&amp;""))&gt;=2,0,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))&gt;=2,1,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))&gt;=2,2,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))&gt;=2,3,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))&gt;=2,4,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))&gt;=2,5,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))&gt;=2,6,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))&gt;=2,7,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))&gt;=2,8,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;""))&gt;=2,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
         <v>2</v>
       </c>
       <c r="E8" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;"")))&lt;3,"",IF(ISNUMBER(SEARCH("0",$A8&amp;""))&gt;=3,0,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))&gt;=3,1,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))&gt;=3,2,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))&gt;=3,3,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))&gt;=3,4,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))&gt;=3,5,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))&gt;=3,6,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))&gt;=3,7,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))&gt;=3,8,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;""))&gt;=3,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
       <c r="F8" s="3" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;"")))&lt;4,"",IF(ISNUMBER(SEARCH("0",$A8&amp;""))&gt;=4,0,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))&gt;=4,1,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))&gt;=4,2,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))&gt;=4,3,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))&gt;=4,4,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))&gt;=4,5,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))&gt;=4,6,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))&gt;=4,7,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))&gt;=4,8,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;""))&gt;=4,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
       <c r="G8" s="4" t="str">
-        <f aca="false">IF((ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;"")))&lt;5,"",IF(ISNUMBER(SEARCH("0",$A8&amp;""))&gt;=5,0,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))&gt;=5,1,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))&gt;=5,2,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))&gt;=5,3,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))&gt;=5,4,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))&gt;=5,5,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))&gt;=5,6,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))&gt;=5,7,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))&gt;=5,8,IF(ISNUMBER(SEARCH("0",$A8&amp;""))+ISNUMBER(SEARCH("1",$A8&amp;""))+ISNUMBER(SEARCH("2",$A8&amp;""))+ISNUMBER(SEARCH("3",$A8&amp;""))+ISNUMBER(SEARCH("4",$A8&amp;""))+ISNUMBER(SEARCH("5",$A8&amp;""))+ISNUMBER(SEARCH("6",$A8&amp;""))+ISNUMBER(SEARCH("7",$A8&amp;""))+ISNUMBER(SEARCH("8",$A8&amp;""))+ISNUMBER(SEARCH("9",$A8&amp;""))&gt;=5,9,"))))))))))))))))))))))</f>
+        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
         <v/>
       </c>
     </row>

--- a/outputs/41420.xlsx
+++ b/outputs/41420.xlsx
@@ -20,24 +20,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
   <si>
     <t xml:space="preserve">505</t>
   </si>
   <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
     <t xml:space="preserve">8247</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
     <t xml:space="preserve">7237</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">2368</t>
   </si>
   <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
     <t xml:space="preserve">0249</t>
   </si>
   <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
     <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">122</t>
@@ -135,7 +165,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,182 +370,127 @@
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A2)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A2)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A2)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A2)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A2)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A2)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A2)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A2)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A2)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A2)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>8</v>
-      </c>
-      <c r="G3" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A3)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A3)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A3)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A3)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A3)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A3)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A3)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A3)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A3)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A3)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>7</v>
-      </c>
-      <c r="F4" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A4)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A4)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A4)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A4)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A4)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A4)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A4)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A4)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A4)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A4)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>8</v>
-      </c>
-      <c r="G5" s="4" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A5)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A5)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A5)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A5)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A5)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A5)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A5)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A5)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A5)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A5)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>4</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>9</v>
-      </c>
-      <c r="G6" s="4" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A6)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A6)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A6)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A6)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A6)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A6)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A6)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A6)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A6)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A6)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="E6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
+      <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="4" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A7)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A7)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A7)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A7)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A7)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A7)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A7)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A7)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A7)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A7)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
-        <v>2</v>
-      </c>
-      <c r="E8" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="3" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f aca="false">IFERROR(VALUE(MID(IF(ISNUMBER(SEARCH("0",$A8)),"0","")&amp;IF(ISNUMBER(SEARCH("1",$A8)),"1","")&amp;IF(ISNUMBER(SEARCH("2",$A8)),"2","")&amp;IF(ISNUMBER(SEARCH("3",$A8)),"3","")&amp;IF(ISNUMBER(SEARCH("4",$A8)),"4","")&amp;IF(ISNUMBER(SEARCH("5",$A8)),"5","")&amp;IF(ISNUMBER(SEARCH("6",$A8)),"6","")&amp;IF(ISNUMBER(SEARCH("7",$A8)),"7","")&amp;IF(ISNUMBER(SEARCH("8",$A8)),"8","")&amp;IF(ISNUMBER(SEARCH("9",$A8)),"9",""),COLUMN()-2,1)),"")</f>
-        <v/>
-      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
